--- a/part3/див портфель.xlsx
+++ b/part3/див портфель.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usual\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usual\Code\InvestmentAnalysisAndPortfolioInvesting\part3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370C0D29-C1B9-4A7E-81DD-EB26CB81305C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86512209-EE28-487E-8103-A38789D95DF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="55">
   <si>
     <t>Компания</t>
   </si>
@@ -128,30 +128,9 @@
     <t>SNGSP</t>
   </si>
   <si>
-    <t>Портфель для ленивого, с низко-умеренным риском, но приемлемой доходностью</t>
-  </si>
-  <si>
-    <t>Остальные компании индекса имеют метрику &lt; 1,0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дабы дифференцироваать ценные бумаги, не берем НОВАТЭК и Татнефть; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Полюс - риск, тк зависит от цен на золото, которые находятся вблизи исторических максимумов; </t>
-  </si>
-  <si>
-    <t>ВТБ с 2022 платил дивиденды лишь один раз, не факт, что такое продолжится, лучше взять СБЕР, который платит дивы ежегодно</t>
-  </si>
-  <si>
-    <t>В качестве пятой компании берем Мос биржу в качестве большей дифференцированности</t>
-  </si>
-  <si>
     <t>TTM = Trailing Twelve Months — «скользящие 12 месяцев». Берутся данные не за календарный год, а за любые последние 12 месяцев</t>
   </si>
   <si>
-    <t>Х5 берем т.к. дивы не платились изза редомициляции</t>
-  </si>
-  <si>
     <t>Доходность</t>
   </si>
   <si>
@@ -216,6 +195,12 @@
   </si>
   <si>
     <t>Низко-умеренный</t>
+  </si>
+  <si>
+    <t>Метрика &gt; 1</t>
+  </si>
+  <si>
+    <t>Портфель</t>
   </si>
 </sst>
 </file>
@@ -260,7 +245,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +279,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -391,7 +388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -418,15 +415,6 @@
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -442,23 +430,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -467,13 +446,20 @@
     <xf numFmtId="10" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -481,6 +467,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC85600"/>
+      <color rgb="FFFF3300"/>
+      <color rgb="FF964000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -507,6 +500,39 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Доли</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0"/>
+              <a:t> секторов в </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>%</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -546,7 +572,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$C$33</c:f>
+              <c:f>Лист1!$O$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -569,6 +595,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-D2E6-4C2C-8C0B-B73544E937A2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -584,6 +615,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-D2E6-4C2C-8C0B-B73544E937A2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -599,6 +635,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-D2E6-4C2C-8C0B-B73544E937A2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -614,6 +655,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-D2E6-4C2C-8C0B-B73544E937A2}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -673,7 +719,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$B$34:$B$37</c:f>
+              <c:f>Лист1!$N$16:$N$19</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -693,7 +739,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$C$34:$C$37</c:f>
+              <c:f>Лист1!$O$16:$O$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -868,7 +914,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$J$24</c:f>
+              <c:f>Лист1!$J$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -887,9 +933,106 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-3625-4D09-8564-C4732CCCB52A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF3300"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-3625-4D09-8564-C4732CCCB52A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-3625-4D09-8564-C4732CCCB52A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3625-4D09-8564-C4732CCCB52A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C85600"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-3625-4D09-8564-C4732CCCB52A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$A$25:$A$29</c:f>
+              <c:f>Лист1!$A$16:$A$20</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -912,7 +1055,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$J$25:$J$29</c:f>
+              <c:f>Лист1!$J$16:$J$20</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1168,7 +1311,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Лист1!$I$24</c:f>
+              <c:f>Лист1!$I$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1187,9 +1330,106 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="92D050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6021-4011-99AB-04A078CEC625}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF3300"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-6021-4011-99AB-04A078CEC625}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-6021-4011-99AB-04A078CEC625}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6021-4011-99AB-04A078CEC625}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C85600"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-6021-4011-99AB-04A078CEC625}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Лист1!$A$25:$A$29</c:f>
+              <c:f>Лист1!$A$16:$A$20</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1212,7 +1452,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Лист1!$I$25:$I$29</c:f>
+              <c:f>Лист1!$I$16:$I$20</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -3061,16 +3301,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>104776</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3097,16 +3337,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3133,16 +3373,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3165,6 +3405,174 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Прямая со стрелкой 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03B42C94-7763-9629-40A6-078F21F4B1FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13115925" y="3819525"/>
+          <a:ext cx="1076325" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Прямая со стрелкой 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F65F4B1-1933-FC88-FE60-3E2A87E97159}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4714875" y="4867275"/>
+          <a:ext cx="3181350" cy="600075"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Прямая со стрелкой 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD4DB496-E5BF-8861-3A8B-C99E8C2BC060}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="8467725" y="4829175"/>
+          <a:ext cx="19050" cy="695325"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3439,6 +3847,7 @@
     <col min="1" max="2" width="18.140625" customWidth="1"/>
     <col min="3" max="10" width="12.85546875" customWidth="1"/>
     <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" customWidth="1"/>
     <col min="16" max="16" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3458,7 +3867,7 @@
       <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G1" s="6" t="s">
@@ -3470,11 +3879,11 @@
       <c r="I1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="K1" s="18"/>
-      <c r="P1" s="10"/>
+      <c r="J1" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3483,35 +3892,35 @@
       <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="15">
         <v>0</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="15">
         <v>648</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="16">
         <v>641</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="11">
         <v>1016</v>
       </c>
       <c r="G2" s="8">
         <v>2420</v>
       </c>
-      <c r="H2" s="15">
-        <f>SQRT(G2)</f>
+      <c r="H2" s="12">
+        <f t="shared" ref="H2:H12" si="0">SQRT(G2)</f>
         <v>49.193495504995376</v>
       </c>
       <c r="I2" s="9">
-        <f>F2/H2</f>
+        <f t="shared" ref="I2:I12" si="1">F2/H2</f>
         <v>20.653136955816237</v>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="19">
         <f>F2/G2</f>
         <v>0.41983471074380163</v>
       </c>
-      <c r="P2" t="s">
-        <v>36</v>
+      <c r="L2" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3521,35 +3930,35 @@
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="15">
         <v>885</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="15">
         <v>1012</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="16">
         <v>938</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="11">
         <v>938</v>
       </c>
       <c r="G3" s="8">
         <v>5140</v>
       </c>
-      <c r="H3" s="15">
-        <f>SQRT(G3)</f>
+      <c r="H3" s="12">
+        <f t="shared" si="0"/>
         <v>71.693793315739683</v>
       </c>
       <c r="I3" s="9">
-        <f>F3/H3</f>
+        <f t="shared" si="1"/>
         <v>13.083419869681677</v>
       </c>
-      <c r="J3" s="25">
-        <f t="shared" ref="J3:J12" si="0">F3/G3</f>
+      <c r="J3" s="19">
+        <f t="shared" ref="J3:J12" si="2">F3/G3</f>
         <v>0.18249027237354085</v>
       </c>
       <c r="K3" s="1"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -3558,35 +3967,35 @@
       <c r="B4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="15">
         <v>1020</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="15">
         <v>552</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="16">
         <v>360</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="11">
         <v>360</v>
       </c>
       <c r="G4" s="8">
         <v>6900</v>
       </c>
-      <c r="H4" s="15">
-        <f>SQRT(G4)</f>
+      <c r="H4" s="12">
+        <f t="shared" si="0"/>
         <v>83.066238629180745</v>
       </c>
-      <c r="I4" s="13">
-        <f>F4/H4</f>
+      <c r="I4" s="10">
+        <f t="shared" si="1"/>
         <v>4.3338907110876912</v>
       </c>
-      <c r="J4" s="26">
-        <f t="shared" si="0"/>
+      <c r="J4" s="20">
+        <f t="shared" si="2"/>
         <v>5.2173913043478258E-2</v>
       </c>
       <c r="K4" s="2"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3595,35 +4004,35 @@
       <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="15">
         <v>0</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="15">
         <v>130</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="16">
         <v>180</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="11">
         <v>180</v>
       </c>
       <c r="G5" s="8">
         <v>2481</v>
       </c>
-      <c r="H5" s="15">
-        <f>SQRT(G5)</f>
+      <c r="H5" s="12">
+        <f t="shared" si="0"/>
         <v>49.809637621649088</v>
       </c>
-      <c r="I5" s="13">
-        <f>F5/H5</f>
+      <c r="I5" s="10">
+        <f t="shared" si="1"/>
         <v>3.6137584731547099</v>
       </c>
-      <c r="J5" s="26">
-        <f t="shared" si="0"/>
+      <c r="J5" s="20">
+        <f t="shared" si="2"/>
         <v>7.2551390568319232E-2</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -3632,35 +4041,35 @@
       <c r="B6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="15">
         <v>0</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="15">
         <v>0</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="16">
         <v>25.58</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="11">
         <v>25.58</v>
       </c>
       <c r="G6" s="8">
         <v>87.3</v>
       </c>
-      <c r="H6" s="15">
-        <f>SQRT(G6)</f>
+      <c r="H6" s="12">
+        <f t="shared" si="0"/>
         <v>9.3434469014384618</v>
       </c>
-      <c r="I6" s="13">
-        <f>F6/H6</f>
+      <c r="I6" s="10">
+        <f t="shared" si="1"/>
         <v>2.737747671692965</v>
       </c>
-      <c r="J6" s="26">
-        <f t="shared" si="0"/>
+      <c r="J6" s="20">
+        <f t="shared" si="2"/>
         <v>0.29301260022909509</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -3669,72 +4078,72 @@
       <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="15">
         <v>95.08</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="15">
         <v>79.59</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="16">
         <v>82.15</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="11">
         <v>82.15</v>
       </c>
       <c r="G7" s="8">
         <v>1185</v>
       </c>
-      <c r="H7" s="15">
-        <f>SQRT(G7)</f>
+      <c r="H7" s="12">
+        <f t="shared" si="0"/>
         <v>34.423828956117013</v>
       </c>
-      <c r="I7" s="13">
-        <f>F7/H7</f>
+      <c r="I7" s="10">
+        <f t="shared" si="1"/>
         <v>2.3864283111772258</v>
       </c>
-      <c r="J7" s="26">
-        <f t="shared" si="0"/>
+      <c r="J7" s="20">
+        <f t="shared" si="2"/>
         <v>6.9324894514767935E-2</v>
       </c>
       <c r="K7" s="3"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="19">
+        <v>35</v>
+      </c>
+      <c r="C8" s="15">
         <v>62.11</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="17">
         <v>98.54</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <v>82.92</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>65.59</v>
       </c>
       <c r="G8" s="8">
         <v>540</v>
       </c>
-      <c r="H8" s="15">
-        <f>SQRT(G8)</f>
+      <c r="H8" s="12">
+        <f t="shared" si="0"/>
         <v>23.2379000772445</v>
       </c>
-      <c r="I8" s="13">
-        <f>F8/H8</f>
+      <c r="I8" s="10">
+        <f t="shared" si="1"/>
         <v>2.8225441964193831</v>
       </c>
-      <c r="J8" s="26">
-        <f t="shared" si="0"/>
+      <c r="J8" s="20">
+        <f t="shared" si="2"/>
         <v>0.12146296296296297</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -3743,35 +4152,35 @@
       <c r="B9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="15">
         <v>25</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="15">
         <v>33.299999999999997</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="16">
         <v>34.840000000000003</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="11">
         <v>34.840000000000003</v>
       </c>
       <c r="G9" s="8">
         <v>316</v>
       </c>
-      <c r="H9" s="15">
-        <f>SQRT(G9)</f>
+      <c r="H9" s="12">
+        <f t="shared" si="0"/>
         <v>17.776388834631177</v>
       </c>
       <c r="I9" s="9">
-        <f>F9/H9</f>
+        <f t="shared" si="1"/>
         <v>1.9599031234131339</v>
       </c>
-      <c r="J9" s="25">
-        <f t="shared" si="0"/>
+      <c r="J9" s="19">
+        <f t="shared" si="2"/>
         <v>0.11025316455696203</v>
       </c>
       <c r="K9" s="4"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -3780,35 +4189,35 @@
       <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="15">
         <v>4.84</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="15">
         <v>17.350000000000001</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="16">
         <v>26.11</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="11">
         <v>26.11</v>
       </c>
       <c r="G10" s="8">
         <v>183.3</v>
       </c>
-      <c r="H10" s="15">
-        <f>SQRT(G10)</f>
+      <c r="H10" s="12">
+        <f t="shared" si="0"/>
         <v>13.538833036861043</v>
       </c>
       <c r="I10" s="9">
-        <f>F10/H10</f>
+        <f t="shared" si="1"/>
         <v>1.9285266262544563</v>
       </c>
-      <c r="J10" s="25">
-        <f t="shared" si="0"/>
+      <c r="J10" s="19">
+        <f t="shared" si="2"/>
         <v>0.14244408074195308</v>
       </c>
       <c r="K10" s="2"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -3817,35 +4226,35 @@
       <c r="B11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="15">
         <v>38.369999999999997</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="15">
         <v>59.78</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="16">
         <v>51.15</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="11">
         <v>26.24</v>
       </c>
       <c r="G11" s="8">
         <v>390</v>
       </c>
-      <c r="H11" s="15">
-        <f>SQRT(G11)</f>
+      <c r="H11" s="12">
+        <f t="shared" si="0"/>
         <v>19.748417658131498</v>
       </c>
-      <c r="I11" s="13">
-        <f>F11/H11</f>
+      <c r="I11" s="10">
+        <f t="shared" si="1"/>
         <v>1.3287140496137706</v>
       </c>
-      <c r="J11" s="26">
-        <f t="shared" si="0"/>
+      <c r="J11" s="20">
+        <f t="shared" si="2"/>
         <v>6.7282051282051281E-2</v>
       </c>
       <c r="K11" s="4"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -3854,37 +4263,40 @@
       <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="15">
         <v>0.8</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="15">
         <v>12.29</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="16">
         <v>8.5</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="11">
         <v>8.5</v>
       </c>
       <c r="G12" s="8">
         <v>45.3</v>
       </c>
-      <c r="H12" s="15">
-        <f>SQRT(G12)</f>
+      <c r="H12" s="12">
+        <f t="shared" si="0"/>
         <v>6.730527468185536</v>
       </c>
       <c r="I12" s="9">
-        <f>F12/H12</f>
+        <f t="shared" si="1"/>
         <v>1.2629025050679261</v>
       </c>
-      <c r="J12" s="25">
-        <f t="shared" si="0"/>
+      <c r="J12" s="19">
+        <f t="shared" si="2"/>
         <v>0.18763796909492275</v>
       </c>
       <c r="K12" s="4"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="2"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="29" t="s">
+        <v>53</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -3896,9 +4308,7 @@
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A14" s="5"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -3909,371 +4319,294 @@
       <c r="K14" s="3"/>
       <c r="P14" s="2"/>
     </row>
-    <row r="15" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="3"/>
+    <row r="15" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>37</v>
+      </c>
       <c r="P15" s="2"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="4"/>
+      <c r="A16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="15">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15">
+        <v>648</v>
+      </c>
+      <c r="E16" s="16">
+        <v>641</v>
+      </c>
+      <c r="F16" s="11">
+        <v>1016</v>
+      </c>
+      <c r="G16" s="8">
+        <v>2420</v>
+      </c>
+      <c r="H16" s="12">
+        <f>SQRT(G16)</f>
+        <v>49.193495504995376</v>
+      </c>
+      <c r="I16" s="9">
+        <f>F16/H16</f>
+        <v>20.653136955816237</v>
+      </c>
+      <c r="J16" s="19">
+        <f>F16/G16</f>
+        <v>0.41983471074380163</v>
+      </c>
+      <c r="K16" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="O16" s="24">
+        <v>40</v>
+      </c>
       <c r="P16" s="2"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="3"/>
+      <c r="A17" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="15">
+        <v>885</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1012</v>
+      </c>
+      <c r="E17" s="16">
+        <v>938</v>
+      </c>
+      <c r="F17" s="11">
+        <v>938</v>
+      </c>
+      <c r="G17" s="8">
+        <v>5140</v>
+      </c>
+      <c r="H17" s="12">
+        <f>SQRT(G17)</f>
+        <v>71.693793315739683</v>
+      </c>
+      <c r="I17" s="9">
+        <f>F17/H17</f>
+        <v>13.083419869681677</v>
+      </c>
+      <c r="J17" s="19">
+        <f t="shared" ref="J17:J20" si="3">F17/G17</f>
+        <v>0.18249027237354085</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="N17" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="O17" s="24">
+        <v>20</v>
+      </c>
       <c r="P17" s="2"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="3"/>
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="15">
+        <v>25</v>
+      </c>
+      <c r="D18" s="15">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="E18" s="16">
+        <v>34.840000000000003</v>
+      </c>
+      <c r="F18" s="11">
+        <v>34.840000000000003</v>
+      </c>
+      <c r="G18" s="8">
+        <v>316</v>
+      </c>
+      <c r="H18" s="12">
+        <f>SQRT(G18)</f>
+        <v>17.776388834631177</v>
+      </c>
+      <c r="I18" s="9">
+        <f>F18/H18</f>
+        <v>1.9599031234131339</v>
+      </c>
+      <c r="J18" s="19">
+        <f t="shared" si="3"/>
+        <v>0.11025316455696203</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="N18" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="O18" s="24">
+        <v>20</v>
+      </c>
       <c r="P18" s="2"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+    <row r="19" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="15">
+        <v>4.84</v>
+      </c>
+      <c r="D19" s="15">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="E19" s="16">
+        <v>26.11</v>
+      </c>
+      <c r="F19" s="11">
+        <v>26.11</v>
+      </c>
+      <c r="G19" s="8">
+        <v>183.3</v>
+      </c>
+      <c r="H19" s="12">
+        <f>SQRT(G19)</f>
+        <v>13.538833036861043</v>
+      </c>
+      <c r="I19" s="9">
+        <f>F19/H19</f>
+        <v>1.9285266262544563</v>
+      </c>
+      <c r="J19" s="19">
+        <f t="shared" si="3"/>
+        <v>0.14244408074195308</v>
+      </c>
+      <c r="K19" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="N19" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="O19" s="24">
+        <v>20</v>
+      </c>
       <c r="P19" s="2"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>37</v>
+    <row r="20" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="D20" s="15">
+        <v>12.29</v>
+      </c>
+      <c r="E20" s="16">
+        <v>8.5</v>
+      </c>
+      <c r="F20" s="11">
+        <v>8.5</v>
+      </c>
+      <c r="G20" s="8">
+        <v>45.3</v>
+      </c>
+      <c r="H20" s="12">
+        <f>SQRT(G20)</f>
+        <v>6.730527468185536</v>
+      </c>
+      <c r="I20" s="9">
+        <f>F20/H20</f>
+        <v>1.2629025050679261</v>
+      </c>
+      <c r="J20" s="21">
+        <f t="shared" si="3"/>
+        <v>0.18763796909492275</v>
+      </c>
+      <c r="K20" s="18">
+        <v>0.2</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="6" t="s">
+    <row r="21" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="22">
+        <f>AVERAGE(J16:J20)</f>
+        <v>0.20853203950223609</v>
+      </c>
+      <c r="K21" s="23">
+        <f>SUM(K16:K20)</f>
         <v>1</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J24" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="K24" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="19">
-        <v>0</v>
-      </c>
-      <c r="D25" s="19">
-        <v>648</v>
-      </c>
-      <c r="E25" s="20">
-        <v>641</v>
-      </c>
-      <c r="F25" s="14">
-        <v>1016</v>
-      </c>
-      <c r="G25" s="8">
-        <v>2420</v>
-      </c>
-      <c r="H25" s="15">
-        <f>SQRT(G25)</f>
-        <v>49.193495504995376</v>
-      </c>
-      <c r="I25" s="9">
-        <f>F25/H25</f>
-        <v>20.653136955816237</v>
-      </c>
-      <c r="J25" s="25">
-        <f>F25/G25</f>
-        <v>0.41983471074380163</v>
-      </c>
-      <c r="K25" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="19">
-        <v>885</v>
-      </c>
-      <c r="D26" s="19">
-        <v>1012</v>
-      </c>
-      <c r="E26" s="20">
-        <v>938</v>
-      </c>
-      <c r="F26" s="14">
-        <v>938</v>
-      </c>
-      <c r="G26" s="8">
-        <v>5140</v>
-      </c>
-      <c r="H26" s="15">
-        <f>SQRT(G26)</f>
-        <v>71.693793315739683</v>
-      </c>
-      <c r="I26" s="9">
-        <f>F26/H26</f>
-        <v>13.083419869681677</v>
-      </c>
-      <c r="J26" s="25">
-        <f t="shared" ref="J26:J29" si="1">F26/G26</f>
-        <v>0.18249027237354085</v>
-      </c>
-      <c r="K26" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="19">
-        <v>25</v>
-      </c>
-      <c r="D27" s="19">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="E27" s="20">
-        <v>34.840000000000003</v>
-      </c>
-      <c r="F27" s="14">
-        <v>34.840000000000003</v>
-      </c>
-      <c r="G27" s="8">
-        <v>316</v>
-      </c>
-      <c r="H27" s="15">
-        <f>SQRT(G27)</f>
-        <v>17.776388834631177</v>
-      </c>
-      <c r="I27" s="9">
-        <f>F27/H27</f>
-        <v>1.9599031234131339</v>
-      </c>
-      <c r="J27" s="25">
-        <f t="shared" si="1"/>
-        <v>0.11025316455696203</v>
-      </c>
-      <c r="K27" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C28" s="19">
-        <v>4.84</v>
-      </c>
-      <c r="D28" s="19">
-        <v>17.350000000000001</v>
-      </c>
-      <c r="E28" s="20">
-        <v>26.11</v>
-      </c>
-      <c r="F28" s="14">
-        <v>26.11</v>
-      </c>
-      <c r="G28" s="8">
-        <v>183.3</v>
-      </c>
-      <c r="H28" s="15">
-        <f>SQRT(G28)</f>
-        <v>13.538833036861043</v>
-      </c>
-      <c r="I28" s="9">
-        <f>F28/H28</f>
-        <v>1.9285266262544563</v>
-      </c>
-      <c r="J28" s="25">
-        <f t="shared" si="1"/>
-        <v>0.14244408074195308</v>
-      </c>
-      <c r="K28" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="19">
-        <v>0.8</v>
-      </c>
-      <c r="D29" s="19">
-        <v>12.29</v>
-      </c>
-      <c r="E29" s="20">
-        <v>8.5</v>
-      </c>
-      <c r="F29" s="14">
-        <v>8.5</v>
-      </c>
-      <c r="G29" s="8">
-        <v>45.3</v>
-      </c>
-      <c r="H29" s="15">
-        <f>SQRT(G29)</f>
-        <v>6.730527468185536</v>
-      </c>
-      <c r="I29" s="9">
-        <f>F29/H29</f>
-        <v>1.2629025050679261</v>
-      </c>
-      <c r="J29" s="27">
-        <f t="shared" si="1"/>
-        <v>0.18763796909492275</v>
-      </c>
-      <c r="K29" s="24">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="I30" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="28">
-        <f>AVERAGE(J25:J29)</f>
-        <v>0.20853203950223609</v>
-      </c>
-      <c r="K30" s="29">
-        <f>SUM(K25:K29)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34" s="30">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="30">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C36" s="30">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C37" s="30">
-        <v>20</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D51" s="1"/>
     </row>
     <row r="52" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C52" s="2">
         <v>5</v>
@@ -4282,46 +4615,46 @@
     </row>
     <row r="53" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="33">
+        <v>45</v>
+      </c>
+      <c r="C53" s="26">
         <v>0.2</v>
       </c>
       <c r="D53" s="2"/>
     </row>
     <row r="54" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" s="32">
+        <v>46</v>
+      </c>
+      <c r="C54" s="25">
         <v>0.20849999999999999</v>
       </c>
       <c r="D54" s="2"/>
     </row>
     <row r="55" spans="2:4" ht="75" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D55" s="2"/>
     </row>
     <row r="56" spans="2:4" ht="45" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2"/>
     </row>
     <row r="57" spans="2:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B57" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D57" s="2"/>
     </row>
